--- a/data/trans_orig/IP19C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75887</t>
+          <t>76137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160066</t>
+          <t>160079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82696</t>
+          <t>81860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>92891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>95834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103558</t>
+          <t>103128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>182064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194448</t>
+          <t>194390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>40729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>50424</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123372</t>
+          <t>122768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140337</t>
+          <t>139134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134794</t>
+          <t>134452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151169</t>
+          <t>151051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264570</t>
+          <t>263833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286546</t>
+          <t>286773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297214</t>
+          <t>297809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317682</t>
+          <t>316795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315738</t>
+          <t>315423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>334592</t>
+          <t>333558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>618308</t>
+          <t>618565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>646219</t>
+          <t>646042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,77 +3043,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7552</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8267</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3046</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7425</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8791</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73901</t>
+          <t>73412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,82 +3151,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>89018</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>84512</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91388</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>165958</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>161484</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>168372</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>95,13%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>89018</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>84639</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91387</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>165958</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>160960</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>168432</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111385</t>
+          <t>111014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120588</t>
+          <t>120938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114098</t>
+          <t>114570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125099</t>
+          <t>124984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230032</t>
+          <t>230275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243457</t>
+          <t>244020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114206</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129438</t>
+          <t>128840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111583</t>
+          <t>112366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>125902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231778</t>
+          <t>232108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252344</t>
+          <t>252412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>310733</t>
+          <t>310867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328970</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318727</t>
+          <t>319264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>337950</t>
+          <t>338256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>635712</t>
+          <t>636051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>662412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76600</t>
+          <t>76492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81546</t>
+          <t>81542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143777</t>
+          <t>143627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149048</t>
+          <t>149083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140638</t>
+          <t>140268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147662</t>
+          <t>147664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138172</t>
+          <t>138778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146552</t>
+          <t>146491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281658</t>
+          <t>282390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292784</t>
+          <t>292452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>48404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112131</t>
+          <t>112490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127557</t>
+          <t>128193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>116989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127487</t>
+          <t>127958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234055</t>
+          <t>232734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252616</t>
+          <t>252679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323424</t>
+          <t>323401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342023</t>
+          <t>341848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338732</t>
+          <t>339054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>353151</t>
+          <t>353520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668499</t>
+          <t>668272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>691661</t>
+          <t>690667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61610</t>
+          <t>61274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71862</t>
+          <t>70760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>76740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134916</t>
+          <t>135288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142141</t>
+          <t>142138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113708</t>
+          <t>113644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120501</t>
+          <t>120457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146995</t>
+          <t>147353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158991</t>
+          <t>159114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263389</t>
+          <t>264913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278345</t>
+          <t>278087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>34692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52328</t>
+          <t>54113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164336</t>
+          <t>163045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180629</t>
+          <t>180334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212482</t>
+          <t>213085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227404</t>
+          <t>227794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382617</t>
+          <t>380832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403411</t>
+          <t>403673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>350576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368447</t>
+          <t>369561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445478</t>
+          <t>446203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465045</t>
+          <t>464469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>804466</t>
+          <t>804047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830394</t>
+          <t>830260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3138</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,107 +1066,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4661</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4342</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79097</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75757</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79097</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>248</t>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160079</t>
+          <t>160411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9194</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10980</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6302</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17333</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16515</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4945</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2591</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9885</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>100774</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>96525</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103746</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>88213</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81860</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92891</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82678</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92720</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>100774</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95834</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>103128</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182064</t>
+          <t>182477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194390</t>
+          <t>194872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29960</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38405</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>31150</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24363</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40729</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23344</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40776</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29960</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39249</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73364</t>
+          <t>73358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143741</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135296</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>151260</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>132347</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>122768</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>139134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>122721</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>140153</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>143741</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>134452</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>151051</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263833</t>
+          <t>263839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286773</t>
+          <t>286326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27746</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34135</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53121</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32872</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>52969</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28173</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>325504</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315032</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>333985</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>308032</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>297809</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>316795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>297961</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>318058</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>325504</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>315423</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>333558</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>618565</t>
+          <t>619604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>647346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7335</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4276</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3046</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7552</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89018</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84729</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91370</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>76941</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73412</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>73945</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>89018</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>84512</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91388</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>229</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>161596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168372</t>
+          <t>168455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7043</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17613</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14808</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14339</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11546</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17516</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120540</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114473</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>125043</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>117160</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111014</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>111483</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>120973</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,12%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>120540</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114570</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>124984</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230275</t>
+          <t>229701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244020</t>
+          <t>243871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16063</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29792</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24929</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19080</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33765</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18611</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33692</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21560</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15281</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28817</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>37594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>58179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119623</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111391</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>125120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>122991</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>114155</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128840</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>114228</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>129309</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>83,15%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>119623</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>112366</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>125902</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232108</t>
+          <t>230924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252412</t>
+          <t>251509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46512</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25853</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43860</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44516</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27746</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46738</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84678</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>329849</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>319490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>338350</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>455</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>320390</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>310867</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>328874</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>310211</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>328357</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>329849</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>319264</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>338256</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>636051</t>
+          <t>635121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662412</t>
+          <t>662378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>354727</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>682</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5637</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79821</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76222</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81530</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>67378</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64748</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63971</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79821</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76492</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>81542</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143627</t>
+          <t>143464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149083</t>
+          <t>149070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11918</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3754</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8649</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6293</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>16288</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>10046</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>5806</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>15868</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5416,107 +5416,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143048</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146457</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>145163</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140268</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147664</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>140430</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>147710</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>143048</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138778</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146491</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>288212</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>281970</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>292550</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,54%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,09%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>288212</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>282390</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>292452</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18999</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25256</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33393</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18780</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35084</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12295</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7297</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18266</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122960</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127817</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>120627</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112490</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128193</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>110799</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>127103</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>122960</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>116989</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>127958</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232734</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252679</t>
+          <t>252263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29636</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>39995</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21653</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40170</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14488</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28954</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>347113</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>338372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>352994</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>333704</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>323401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341848</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>323226</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>341743</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347113</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>339054</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>353520</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668272</t>
+          <t>668348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>690667</t>
+          <t>690838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>363396</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>19</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4922</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6371</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65846</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62210</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67265</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64716</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>61274</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>62061</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>58448</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63449</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,12%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>75147</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70760</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76740</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>206</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>139864</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135288</t>
+          <t>123229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142138</t>
+          <t>130038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5638</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16753</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1446</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8259</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21778</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>144917</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138545</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149660</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>118112</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113644</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120457</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>154488</t>
+          <t>118210</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147353</t>
+          <t>113741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159114</t>
+          <t>120372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272600</t>
+          <t>263126</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264913</t>
+          <t>255772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278087</t>
+          <t>268235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15808</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25434</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25087</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17403</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34692</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>37381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54113</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>217742</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>208116</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>223536</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>172650</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>163045</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180334</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>221612</t>
+          <t>178465</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213085</t>
+          <t>167535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227794</t>
+          <t>186766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>394261</t>
+          <t>396207</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380832</t>
+          <t>382386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403673</t>
+          <t>406372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19800</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38307</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22072</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41057</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38241</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>45499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>433181</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>422788</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>441295</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>361275</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>350576</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>369561</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>456564</t>
+          <t>364809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446203</t>
+          <t>353368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>464469</t>
+          <t>373431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>817838</t>
+          <t>797989</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>804047</t>
+          <t>784312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830260</t>
+          <t>811873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
